--- a/cypress/fixtures/PerfilEcoProveedor.xlsx
+++ b/cypress/fixtures/PerfilEcoProveedor.xlsx
@@ -16,10 +16,10 @@
     <t>Proveedor</t>
   </si>
   <si>
-    <t>Luis</t>
+    <t>jose manuel</t>
   </si>
   <si>
-    <t>Miguel</t>
+    <t>oscar alfredo</t>
   </si>
 </sst>
 </file>
@@ -43,7 +43,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -52,8 +52,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF4CCCC"/>
-        <bgColor rgb="FFF4CCCC"/>
+        <fgColor rgb="FFCCCCCC"/>
+        <bgColor rgb="FFCCCCCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -70,13 +76,13 @@
     <xf borderId="0" fillId="2" fontId="1" numFmtId="49" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="2" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" vertical="bottom"/>
+    <xf borderId="0" fillId="3" fontId="2" numFmtId="49" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
+    <xf borderId="0" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
   </cellXfs>
